--- a/data/database/lab_processing_scheduler_database.xlsx
+++ b/data/database/lab_processing_scheduler_database.xlsx
@@ -11,9 +11,9 @@
     <sheet name="lists" sheetId="5" state="visible" r:id="rId3"/>
     <sheet name="priority_rules" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="usage_log" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="audit_log" sheetId="2" state="visible" r:id="rId6"/>
-    <sheet name="settings" sheetId="1" state="visible" r:id="rId7"/>
-    <sheet name="reservations" sheetId="9" state="visible" r:id="rId8"/>
+    <sheet name="settings" sheetId="1" state="visible" r:id="rId6"/>
+    <sheet name="reservations" sheetId="9" state="visible" r:id="rId7"/>
+    <sheet name="audit_log" sheetId="10" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">audit_log!$A$1:$I$1</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="475">
   <si>
     <t>user_id</t>
   </si>
@@ -1416,6 +1416,45 @@
   </si>
   <si>
     <t xml:space="preserve">manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-12 19:42:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autorizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin_user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">old_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new_value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_20260512_194209_4447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reservation_approved</t>
   </si>
 </sst>
 </file>
@@ -1435,13 +1474,11 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
       <b/>
     </font>
   </fonts>
@@ -4671,48 +4708,616 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.140625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="33.140625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="51.140625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="82.42578125" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B31" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>10</v>
+      <c r="C31" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{13CD19B6-5C98-44C6-8871-B82A8A418347}"/>
+  <autoFilter ref="A1:D43" xr:uid="{FC5D3631-E584-4234-AC1F-B5BF003CFAF7}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -4722,618 +5327,173 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="33.140625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="51.140625" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="82.42578125" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>20</v>
+      <c r="A1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D1" t="s">
+        <v>419</v>
+      </c>
+      <c r="E1" t="s">
+        <v>420</v>
+      </c>
+      <c r="F1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I1" t="s">
+        <v>424</v>
+      </c>
+      <c r="J1" t="s">
+        <v>425</v>
+      </c>
+      <c r="K1" t="s">
+        <v>426</v>
+      </c>
+      <c r="L1" t="s">
+        <v>427</v>
+      </c>
+      <c r="M1" t="s">
+        <v>428</v>
+      </c>
+      <c r="N1" t="s">
+        <v>429</v>
+      </c>
+      <c r="O1" t="s">
+        <v>430</v>
+      </c>
+      <c r="P1" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>432</v>
+      </c>
+      <c r="R1" t="s">
+        <v>433</v>
+      </c>
+      <c r="S1" t="s">
+        <v>434</v>
+      </c>
+      <c r="T1" t="s">
+        <v>435</v>
+      </c>
+      <c r="U1" t="s">
+        <v>436</v>
+      </c>
+      <c r="V1" t="s">
+        <v>437</v>
+      </c>
+      <c r="W1" t="s">
+        <v>438</v>
+      </c>
+      <c r="X1" t="s">
+        <v>439</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>440</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>441</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>442</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>21</v>
+      <c r="A2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G2" t="s">
+        <v>449</v>
+      </c>
+      <c r="H2" t="s">
+        <v>450</v>
+      </c>
+      <c r="I2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J2" t="s">
+        <v>452</v>
+      </c>
+      <c r="K2" t="s">
+        <v>453</v>
+      </c>
+      <c r="L2" t="s">
+        <v>454</v>
+      </c>
+      <c r="M2" t="s">
+        <v>455</v>
+      </c>
+      <c r="N2" t="s">
+        <v>456</v>
+      </c>
+      <c r="O2" t="s">
+        <v>455</v>
+      </c>
+      <c r="P2" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>458</v>
+      </c>
+      <c r="R2" t="s">
+        <v>459</v>
+      </c>
+      <c r="S2" t="s">
+        <v>463</v>
+      </c>
+      <c r="T2" t="s">
+        <v>461</v>
+      </c>
+      <c r="U2" t="s">
+        <v>464</v>
+      </c>
+      <c r="V2" t="s">
+        <v>462</v>
+      </c>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2" t="s">
+        <v>465</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>458</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D43" xr:uid="{FC5D3631-E584-4234-AC1F-B5BF003CFAF7}"/>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
@@ -5345,160 +5505,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D1" t="s">
         <v>416</v>
       </c>
-      <c r="B1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C1" t="s">
-        <v>418</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>419</v>
       </c>
-      <c r="E1" t="s">
-        <v>420</v>
-      </c>
       <c r="F1" t="s">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="G1" t="s">
-        <v>422</v>
+        <v>470</v>
       </c>
       <c r="H1" t="s">
-        <v>423</v>
+        <v>471</v>
       </c>
       <c r="I1" t="s">
-        <v>424</v>
-      </c>
-      <c r="J1" t="s">
-        <v>425</v>
-      </c>
-      <c r="K1" t="s">
-        <v>426</v>
-      </c>
-      <c r="L1" t="s">
-        <v>427</v>
-      </c>
-      <c r="M1" t="s">
-        <v>428</v>
-      </c>
-      <c r="N1" t="s">
-        <v>429</v>
-      </c>
-      <c r="O1" t="s">
-        <v>430</v>
-      </c>
-      <c r="P1" t="s">
-        <v>431</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>432</v>
-      </c>
-      <c r="R1" t="s">
-        <v>433</v>
-      </c>
-      <c r="S1" t="s">
-        <v>434</v>
-      </c>
-      <c r="T1" t="s">
-        <v>435</v>
-      </c>
-      <c r="U1" t="s">
-        <v>436</v>
-      </c>
-      <c r="V1" t="s">
-        <v>437</v>
-      </c>
-      <c r="W1" t="s">
-        <v>438</v>
-      </c>
-      <c r="X1" t="s">
-        <v>439</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>440</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>441</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>442</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>443</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D2" t="s">
         <v>444</v>
       </c>
-      <c r="B2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C2" t="s">
-        <v>445</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>446</v>
       </c>
-      <c r="E2" t="s">
-        <v>447</v>
-      </c>
       <c r="F2" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="G2" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="H2" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="I2" t="s">
-        <v>451</v>
-      </c>
-      <c r="J2" t="s">
-        <v>452</v>
-      </c>
-      <c r="K2" t="s">
-        <v>453</v>
-      </c>
-      <c r="L2" t="s">
-        <v>454</v>
-      </c>
-      <c r="M2" t="s">
-        <v>455</v>
-      </c>
-      <c r="N2" t="s">
-        <v>456</v>
-      </c>
-      <c r="O2" t="s">
-        <v>455</v>
-      </c>
-      <c r="P2" t="s">
-        <v>457</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>458</v>
-      </c>
-      <c r="R2" t="s">
-        <v>459</v>
-      </c>
-      <c r="S2" t="s">
-        <v>460</v>
-      </c>
-      <c r="T2" t="s">
-        <v>461</v>
-      </c>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
